--- a/CPU Design/CpuAvrAluFlagsExamples.xlsx
+++ b/CPU Design/CpuAvrAluFlagsExamples.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="103" windowWidth="14803" windowHeight="8014"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
   <si>
     <t>Bit</t>
   </si>
@@ -95,12 +95,18 @@
   <si>
     <t>Unsigned numbers when added cause bit 15 to be set</t>
   </si>
+  <si>
+    <t>passed?</t>
+  </si>
+  <si>
+    <t>(SUB)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,16 +122,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -133,11 +157,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -163,207 +203,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="42">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill>
@@ -752,22 +609,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC56"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <dimension ref="A1:AD56"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" customWidth="1"/>
-    <col min="2" max="18" width="2.23046875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="9.3828125" style="6" customWidth="1"/>
-    <col min="20" max="20" width="3.15234375" customWidth="1"/>
-    <col min="21" max="25" width="2.23046875" style="3" customWidth="1"/>
-    <col min="26" max="26" width="2.4609375" customWidth="1"/>
-    <col min="27" max="27" width="53.53515625" customWidth="1"/>
-    <col min="28" max="28" width="27.15234375" style="8" customWidth="1"/>
-    <col min="29" max="29" width="9.921875" style="10" customWidth="1"/>
-    <col min="30" max="30" width="18.69140625" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="18" width="2.21875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.33203125" style="6" customWidth="1"/>
+    <col min="20" max="20" width="3.109375" customWidth="1"/>
+    <col min="21" max="25" width="2.21875" style="3" customWidth="1"/>
+    <col min="26" max="26" width="2.44140625" customWidth="1"/>
+    <col min="27" max="27" width="53.5546875" customWidth="1"/>
+    <col min="28" max="28" width="27.109375" style="8" customWidth="1"/>
+    <col min="29" max="29" width="9.88671875" style="10" customWidth="1"/>
+    <col min="30" max="30" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" ht="15.9">
+    <row r="1" spans="1:30" s="1" customFormat="1" ht="16.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -847,8 +704,11 @@
       <c r="AC1" s="9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -911,8 +771,9 @@
         <f>"0x"&amp;DEC2HEX((B2*2^15)+(C2*2^14)+(D2*2^13)+(E2*2^12)+(F2*2^11)+(G2*2^10)+(H2*2^9)+(I2*2^8)+(J2*2^7)+(K2*2^6)+(L2*2^5)+(M2*2^4)+(N2*2^3)+(O2*2^2)+(P2*2^1)+(Q2*2^0),4)</f>
         <v>0x0008</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AD2" s="16"/>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -975,8 +836,9 @@
         <f>"0x"&amp;DEC2HEX((B3*2^15)+(C3*2^14)+(D3*2^13)+(E3*2^12)+(F3*2^11)+(G3*2^10)+(H3*2^9)+(I3*2^8)+(J3*2^7)+(K3*2^6)+(L3*2^5)+(M3*2^4)+(N3*2^3)+(O3*2^2)+(P3*2^1)+(Q3*2^0),4)</f>
         <v>0x0009</v>
       </c>
-    </row>
-    <row r="4" spans="1:29">
+      <c r="AD3" s="16"/>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1063,8 +925,12 @@
         <f>"0x"&amp;DEC2HEX((B4*2^15)+(C4*2^14)+(D4*2^13)+(E4*2^12)+(F4*2^11)+(G4*2^10)+(H4*2^9)+(I4*2^8)+(J4*2^7)+(K4*2^6)+(L4*2^5)+(M4*2^4)+(N4*2^3)+(O4*2^2)+(P4*2^1)+(Q4*2^0),4)</f>
         <v>0x0011</v>
       </c>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="AD4" s="16"/>
+    </row>
+    <row r="5" spans="1:30">
+      <c r="AD5" s="16"/>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1127,8 +993,9 @@
         <f>"0x"&amp;DEC2HEX((B6*2^15)+(C6*2^14)+(D6*2^13)+(E6*2^12)+(F6*2^11)+(G6*2^10)+(H6*2^9)+(I6*2^8)+(J6*2^7)+(K6*2^6)+(L6*2^5)+(M6*2^4)+(N6*2^3)+(O6*2^2)+(P6*2^1)+(Q6*2^0),4)</f>
         <v>0x4000</v>
       </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AD6" s="16"/>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1191,8 +1058,9 @@
         <f>"0x"&amp;DEC2HEX((B7*2^15)+(C7*2^14)+(D7*2^13)+(E7*2^12)+(F7*2^11)+(G7*2^10)+(H7*2^9)+(I7*2^8)+(J7*2^7)+(K7*2^6)+(L7*2^5)+(M7*2^4)+(N7*2^3)+(O7*2^2)+(P7*2^1)+(Q7*2^0),4)</f>
         <v>0x4000</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7" s="16"/>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1279,8 +1147,12 @@
         <f>"0x"&amp;DEC2HEX((B8*2^15)+(C8*2^14)+(D8*2^13)+(E8*2^12)+(F8*2^11)+(G8*2^10)+(H8*2^9)+(I8*2^8)+(J8*2^7)+(K8*2^6)+(L8*2^5)+(M8*2^4)+(N8*2^3)+(O8*2^2)+(P8*2^1)+(Q8*2^0),4)</f>
         <v>0x8000</v>
       </c>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="AD8" s="16"/>
+    </row>
+    <row r="9" spans="1:30">
+      <c r="AD9" s="16"/>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -1343,8 +1215,9 @@
         <f>"0x"&amp;DEC2HEX((B10*2^15)+(C10*2^14)+(D10*2^13)+(E10*2^12)+(F10*2^11)+(G10*2^10)+(H10*2^9)+(I10*2^8)+(J10*2^7)+(K10*2^6)+(L10*2^5)+(M10*2^4)+(N10*2^3)+(O10*2^2)+(P10*2^1)+(Q10*2^0),4)</f>
         <v>0x8000</v>
       </c>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10" s="16"/>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -1407,8 +1280,9 @@
         <f>"0x"&amp;DEC2HEX((B11*2^15)+(C11*2^14)+(D11*2^13)+(E11*2^12)+(F11*2^11)+(G11*2^10)+(H11*2^9)+(I11*2^8)+(J11*2^7)+(K11*2^6)+(L11*2^5)+(M11*2^4)+(N11*2^3)+(O11*2^2)+(P11*2^1)+(Q11*2^0),4)</f>
         <v>0x8000</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11" s="16"/>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1495,8 +1369,12 @@
         <f>"0x"&amp;DEC2HEX((B12*2^15)+(C12*2^14)+(D12*2^13)+(E12*2^12)+(F12*2^11)+(G12*2^10)+(H12*2^9)+(I12*2^8)+(J12*2^7)+(K12*2^6)+(L12*2^5)+(M12*2^4)+(N12*2^3)+(O12*2^2)+(P12*2^1)+(Q12*2^0),4)</f>
         <v>0x0000</v>
       </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD12" s="16"/>
+    </row>
+    <row r="13" spans="1:30">
+      <c r="AD13" s="16"/>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1559,8 +1437,9 @@
         <f>"0x"&amp;DEC2HEX((B14*2^15)+(C14*2^14)+(D14*2^13)+(E14*2^12)+(F14*2^11)+(G14*2^10)+(H14*2^9)+(I14*2^8)+(J14*2^7)+(K14*2^6)+(L14*2^5)+(M14*2^4)+(N14*2^3)+(O14*2^2)+(P14*2^1)+(Q14*2^0),4)</f>
         <v>0xFFFF</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14" s="16"/>
+    </row>
+    <row r="15" spans="1:30">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -1613,7 +1492,7 @@
         <v>1</v>
       </c>
       <c r="S15" s="6">
-        <f t="shared" ref="S15:S16" si="0" xml:space="preserve"> (-B15*2^15)+(C15*2^14)+(D15*2^13)+(E15*2^12)+(F15*2^11)+(G15*2^10)+(H15*2^9)+(I15*2^8)+(J15*2^7)+(K15*2^6)+(L15*2^5)+(M15*2^4)+(N15*2^3)+(O15*2^2)+(P15*2^1)+(Q15*2^0)</f>
+        <f t="shared" ref="S15" si="0" xml:space="preserve"> (-B15*2^15)+(C15*2^14)+(D15*2^13)+(E15*2^12)+(F15*2^11)+(G15*2^10)+(H15*2^9)+(I15*2^8)+(J15*2^7)+(K15*2^6)+(L15*2^5)+(M15*2^4)+(N15*2^3)+(O15*2^2)+(P15*2^1)+(Q15*2^0)</f>
         <v>-1</v>
       </c>
       <c r="AA15" t="s">
@@ -1623,8 +1502,9 @@
         <f>"0x"&amp;DEC2HEX((B15*2^15)+(C15*2^14)+(D15*2^13)+(E15*2^12)+(F15*2^11)+(G15*2^10)+(H15*2^9)+(I15*2^8)+(J15*2^7)+(K15*2^6)+(L15*2^5)+(M15*2^4)+(N15*2^3)+(O15*2^2)+(P15*2^1)+(Q15*2^0),4)</f>
         <v>0xFFFF</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15" s="16"/>
+    </row>
+    <row r="16" spans="1:30">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1711,8 +1591,12 @@
         <f>"0x"&amp;DEC2HEX((B16*2^15)+(C16*2^14)+(D16*2^13)+(E16*2^12)+(F16*2^11)+(G16*2^10)+(H16*2^9)+(I16*2^8)+(J16*2^7)+(K16*2^6)+(L16*2^5)+(M16*2^4)+(N16*2^3)+(O16*2^2)+(P16*2^1)+(Q16*2^0),4)</f>
         <v>0xFFFE</v>
       </c>
-    </row>
-    <row r="18" spans="1:29">
+      <c r="AD16" s="16"/>
+    </row>
+    <row r="17" spans="1:30">
+      <c r="AD17" s="16"/>
+    </row>
+    <row r="18" spans="1:30">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1775,8 +1659,9 @@
         <f>"0x"&amp;DEC2HEX((B18*2^15)+(C18*2^14)+(D18*2^13)+(E18*2^12)+(F18*2^11)+(G18*2^10)+(H18*2^9)+(I18*2^8)+(J18*2^7)+(K18*2^6)+(L18*2^5)+(M18*2^4)+(N18*2^3)+(O18*2^2)+(P18*2^1)+(Q18*2^0),4)</f>
         <v>0xC000</v>
       </c>
-    </row>
-    <row r="19" spans="1:29">
+      <c r="AD18" s="16"/>
+    </row>
+    <row r="19" spans="1:30">
       <c r="A19" t="s">
         <v>2</v>
       </c>
@@ -1829,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="6">
-        <f t="shared" ref="S19:S20" si="1" xml:space="preserve"> (-B19*2^15)+(C19*2^14)+(D19*2^13)+(E19*2^12)+(F19*2^11)+(G19*2^10)+(H19*2^9)+(I19*2^8)+(J19*2^7)+(K19*2^6)+(L19*2^5)+(M19*2^4)+(N19*2^3)+(O19*2^2)+(P19*2^1)+(Q19*2^0)</f>
+        <f t="shared" ref="S19" si="1" xml:space="preserve"> (-B19*2^15)+(C19*2^14)+(D19*2^13)+(E19*2^12)+(F19*2^11)+(G19*2^10)+(H19*2^9)+(I19*2^8)+(J19*2^7)+(K19*2^6)+(L19*2^5)+(M19*2^4)+(N19*2^3)+(O19*2^2)+(P19*2^1)+(Q19*2^0)</f>
         <v>-16384</v>
       </c>
       <c r="AA19" t="s">
@@ -1839,8 +1724,9 @@
         <f>"0x"&amp;DEC2HEX((B19*2^15)+(C19*2^14)+(D19*2^13)+(E19*2^12)+(F19*2^11)+(G19*2^10)+(H19*2^9)+(I19*2^8)+(J19*2^7)+(K19*2^6)+(L19*2^5)+(M19*2^4)+(N19*2^3)+(O19*2^2)+(P19*2^1)+(Q19*2^0),4)</f>
         <v>0xC000</v>
       </c>
-    </row>
-    <row r="20" spans="1:29">
+      <c r="AD19" s="16"/>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1927,8 +1813,12 @@
         <f>"0x"&amp;DEC2HEX((B20*2^15)+(C20*2^14)+(D20*2^13)+(E20*2^12)+(F20*2^11)+(G20*2^10)+(H20*2^9)+(I20*2^8)+(J20*2^7)+(K20*2^6)+(L20*2^5)+(M20*2^4)+(N20*2^3)+(O20*2^2)+(P20*2^1)+(Q20*2^0),4)</f>
         <v>0x8000</v>
       </c>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AD20" s="16"/>
+    </row>
+    <row r="21" spans="1:30">
+      <c r="AD21" s="16"/>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -1991,8 +1881,9 @@
         <f>"0x"&amp;DEC2HEX((B22*2^15)+(C22*2^14)+(D22*2^13)+(E22*2^12)+(F22*2^11)+(G22*2^10)+(H22*2^9)+(I22*2^8)+(J22*2^7)+(K22*2^6)+(L22*2^5)+(M22*2^4)+(N22*2^3)+(O22*2^2)+(P22*2^1)+(Q22*2^0),4)</f>
         <v>0xC000</v>
       </c>
-    </row>
-    <row r="23" spans="1:29">
+      <c r="AD22" s="16"/>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -2045,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="6">
-        <f t="shared" ref="S23:S24" si="2" xml:space="preserve"> (-B23*2^15)+(C23*2^14)+(D23*2^13)+(E23*2^12)+(F23*2^11)+(G23*2^10)+(H23*2^9)+(I23*2^8)+(J23*2^7)+(K23*2^6)+(L23*2^5)+(M23*2^4)+(N23*2^3)+(O23*2^2)+(P23*2^1)+(Q23*2^0)</f>
+        <f t="shared" ref="S23" si="2" xml:space="preserve"> (-B23*2^15)+(C23*2^14)+(D23*2^13)+(E23*2^12)+(F23*2^11)+(G23*2^10)+(H23*2^9)+(I23*2^8)+(J23*2^7)+(K23*2^6)+(L23*2^5)+(M23*2^4)+(N23*2^3)+(O23*2^2)+(P23*2^1)+(Q23*2^0)</f>
         <v>-16385</v>
       </c>
       <c r="AA23" t="s">
@@ -2055,8 +1946,9 @@
         <f>"0x"&amp;DEC2HEX((B23*2^15)+(C23*2^14)+(D23*2^13)+(E23*2^12)+(F23*2^11)+(G23*2^10)+(H23*2^9)+(I23*2^8)+(J23*2^7)+(K23*2^6)+(L23*2^5)+(M23*2^4)+(N23*2^3)+(O23*2^2)+(P23*2^1)+(Q23*2^0),4)</f>
         <v>0xBFFF</v>
       </c>
-    </row>
-    <row r="24" spans="1:29">
+      <c r="AD23" s="16"/>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -2143,8 +2035,12 @@
         <f>"0x"&amp;DEC2HEX((B24*2^15)+(C24*2^14)+(D24*2^13)+(E24*2^12)+(F24*2^11)+(G24*2^10)+(H24*2^9)+(I24*2^8)+(J24*2^7)+(K24*2^6)+(L24*2^5)+(M24*2^4)+(N24*2^3)+(O24*2^2)+(P24*2^1)+(Q24*2^0),4)</f>
         <v>0x7FFF</v>
       </c>
-    </row>
-    <row r="26" spans="1:29">
+      <c r="AD24" s="16"/>
+    </row>
+    <row r="25" spans="1:30">
+      <c r="AD25" s="16"/>
+    </row>
+    <row r="26" spans="1:30">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -2207,8 +2103,9 @@
         <f>"0x"&amp;DEC2HEX((B26*2^15)+(C26*2^14)+(D26*2^13)+(E26*2^12)+(F26*2^11)+(G26*2^10)+(H26*2^9)+(I26*2^8)+(J26*2^7)+(K26*2^6)+(L26*2^5)+(M26*2^4)+(N26*2^3)+(O26*2^2)+(P26*2^1)+(Q26*2^0),4)</f>
         <v>0xFFF0</v>
       </c>
-    </row>
-    <row r="27" spans="1:29">
+      <c r="AD26" s="16"/>
+    </row>
+    <row r="27" spans="1:30">
       <c r="A27" t="s">
         <v>2</v>
       </c>
@@ -2261,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="6">
-        <f t="shared" ref="S27:S28" si="3" xml:space="preserve"> (-B27*2^15)+(C27*2^14)+(D27*2^13)+(E27*2^12)+(F27*2^11)+(G27*2^10)+(H27*2^9)+(I27*2^8)+(J27*2^7)+(K27*2^6)+(L27*2^5)+(M27*2^4)+(N27*2^3)+(O27*2^2)+(P27*2^1)+(Q27*2^0)</f>
+        <f t="shared" ref="S27" si="3" xml:space="preserve"> (-B27*2^15)+(C27*2^14)+(D27*2^13)+(E27*2^12)+(F27*2^11)+(G27*2^10)+(H27*2^9)+(I27*2^8)+(J27*2^7)+(K27*2^6)+(L27*2^5)+(M27*2^4)+(N27*2^3)+(O27*2^2)+(P27*2^1)+(Q27*2^0)</f>
         <v>6</v>
       </c>
       <c r="AA27" t="s">
@@ -2271,8 +2168,9 @@
         <f>"0x"&amp;DEC2HEX((B27*2^15)+(C27*2^14)+(D27*2^13)+(E27*2^12)+(F27*2^11)+(G27*2^10)+(H27*2^9)+(I27*2^8)+(J27*2^7)+(K27*2^6)+(L27*2^5)+(M27*2^4)+(N27*2^3)+(O27*2^2)+(P27*2^1)+(Q27*2^0),4)</f>
         <v>0x0006</v>
       </c>
-    </row>
-    <row r="28" spans="1:29">
+      <c r="AD27" s="16"/>
+    </row>
+    <row r="28" spans="1:30">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -2356,8 +2254,12 @@
         <f>"0x"&amp;DEC2HEX((B28*2^15)+(C28*2^14)+(D28*2^13)+(E28*2^12)+(F28*2^11)+(G28*2^10)+(H28*2^9)+(I28*2^8)+(J28*2^7)+(K28*2^6)+(L28*2^5)+(M28*2^4)+(N28*2^3)+(O28*2^2)+(P28*2^1)+(Q28*2^0),4)</f>
         <v>0xFFF6</v>
       </c>
-    </row>
-    <row r="30" spans="1:29">
+      <c r="AD28" s="16"/>
+    </row>
+    <row r="29" spans="1:30">
+      <c r="AD29" s="16"/>
+    </row>
+    <row r="30" spans="1:30">
       <c r="A30" t="s">
         <v>1</v>
       </c>
@@ -2420,8 +2322,9 @@
         <f>"0x"&amp;DEC2HEX((B30*2^15)+(C30*2^14)+(D30*2^13)+(E30*2^12)+(F30*2^11)+(G30*2^10)+(H30*2^9)+(I30*2^8)+(J30*2^7)+(K30*2^6)+(L30*2^5)+(M30*2^4)+(N30*2^3)+(O30*2^2)+(P30*2^1)+(Q30*2^0),4)</f>
         <v>0xFFFA</v>
       </c>
-    </row>
-    <row r="31" spans="1:29">
+      <c r="AD30" s="16"/>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31" t="s">
         <v>2</v>
       </c>
@@ -2474,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="6">
-        <f t="shared" ref="S31:S32" si="4" xml:space="preserve"> (-B31*2^15)+(C31*2^14)+(D31*2^13)+(E31*2^12)+(F31*2^11)+(G31*2^10)+(H31*2^9)+(I31*2^8)+(J31*2^7)+(K31*2^6)+(L31*2^5)+(M31*2^4)+(N31*2^3)+(O31*2^2)+(P31*2^1)+(Q31*2^0)</f>
+        <f t="shared" ref="S31" si="4" xml:space="preserve"> (-B31*2^15)+(C31*2^14)+(D31*2^13)+(E31*2^12)+(F31*2^11)+(G31*2^10)+(H31*2^9)+(I31*2^8)+(J31*2^7)+(K31*2^6)+(L31*2^5)+(M31*2^4)+(N31*2^3)+(O31*2^2)+(P31*2^1)+(Q31*2^0)</f>
         <v>6</v>
       </c>
       <c r="AA31" t="s">
@@ -2484,8 +2387,9 @@
         <f>"0x"&amp;DEC2HEX((B31*2^15)+(C31*2^14)+(D31*2^13)+(E31*2^12)+(F31*2^11)+(G31*2^10)+(H31*2^9)+(I31*2^8)+(J31*2^7)+(K31*2^6)+(L31*2^5)+(M31*2^4)+(N31*2^3)+(O31*2^2)+(P31*2^1)+(Q31*2^0),4)</f>
         <v>0x0006</v>
       </c>
-    </row>
-    <row r="32" spans="1:29">
+      <c r="AD31" s="16"/>
+    </row>
+    <row r="32" spans="1:30">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -2569,8 +2473,12 @@
         <f>"0x"&amp;DEC2HEX((B32*2^15)+(C32*2^14)+(D32*2^13)+(E32*2^12)+(F32*2^11)+(G32*2^10)+(H32*2^9)+(I32*2^8)+(J32*2^7)+(K32*2^6)+(L32*2^5)+(M32*2^4)+(N32*2^3)+(O32*2^2)+(P32*2^1)+(Q32*2^0),4)</f>
         <v>0x0000</v>
       </c>
-    </row>
-    <row r="34" spans="1:29">
+      <c r="AD32" s="16"/>
+    </row>
+    <row r="33" spans="1:30">
+      <c r="AD33" s="16"/>
+    </row>
+    <row r="34" spans="1:30">
       <c r="A34" t="s">
         <v>1</v>
       </c>
@@ -2633,8 +2541,9 @@
         <f>"0x"&amp;DEC2HEX((B34*2^15)+(C34*2^14)+(D34*2^13)+(E34*2^12)+(F34*2^11)+(G34*2^10)+(H34*2^9)+(I34*2^8)+(J34*2^7)+(K34*2^6)+(L34*2^5)+(M34*2^4)+(N34*2^3)+(O34*2^2)+(P34*2^1)+(Q34*2^0),4)</f>
         <v>0xFFFA</v>
       </c>
-    </row>
-    <row r="35" spans="1:29">
+      <c r="AD34" s="16"/>
+    </row>
+    <row r="35" spans="1:30">
       <c r="A35" t="s">
         <v>2</v>
       </c>
@@ -2687,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="6">
-        <f t="shared" ref="S35:S36" si="5" xml:space="preserve"> (-B35*2^15)+(C35*2^14)+(D35*2^13)+(E35*2^12)+(F35*2^11)+(G35*2^10)+(H35*2^9)+(I35*2^8)+(J35*2^7)+(K35*2^6)+(L35*2^5)+(M35*2^4)+(N35*2^3)+(O35*2^2)+(P35*2^1)+(Q35*2^0)</f>
+        <f t="shared" ref="S35" si="5" xml:space="preserve"> (-B35*2^15)+(C35*2^14)+(D35*2^13)+(E35*2^12)+(F35*2^11)+(G35*2^10)+(H35*2^9)+(I35*2^8)+(J35*2^7)+(K35*2^6)+(L35*2^5)+(M35*2^4)+(N35*2^3)+(O35*2^2)+(P35*2^1)+(Q35*2^0)</f>
         <v>16</v>
       </c>
       <c r="AA35" t="s">
@@ -2697,8 +2606,9 @@
         <f>"0x"&amp;DEC2HEX((B35*2^15)+(C35*2^14)+(D35*2^13)+(E35*2^12)+(F35*2^11)+(G35*2^10)+(H35*2^9)+(I35*2^8)+(J35*2^7)+(K35*2^6)+(L35*2^5)+(M35*2^4)+(N35*2^3)+(O35*2^2)+(P35*2^1)+(Q35*2^0),4)</f>
         <v>0x0010</v>
       </c>
-    </row>
-    <row r="36" spans="1:29">
+      <c r="AD35" s="16"/>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -2782,8 +2692,43 @@
         <f>"0x"&amp;DEC2HEX((B36*2^15)+(C36*2^14)+(D36*2^13)+(E36*2^12)+(F36*2^11)+(G36*2^10)+(H36*2^9)+(I36*2^8)+(J36*2^7)+(K36*2^6)+(L36*2^5)+(M36*2^4)+(N36*2^3)+(O36*2^2)+(P36*2^1)+(Q36*2^0),4)</f>
         <v>0x000A</v>
       </c>
-    </row>
-    <row r="38" spans="1:29">
+      <c r="AD36" s="16"/>
+    </row>
+    <row r="37" spans="1:30">
+      <c r="A37" s="11"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="12"/>
+      <c r="R37" s="12"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
+      <c r="Z37" s="11"/>
+      <c r="AA37" s="11"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="15"/>
+      <c r="AD37" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38" t="s">
         <v>1</v>
       </c>
@@ -2846,8 +2791,9 @@
         <f>"0x"&amp;DEC2HEX((B38*2^15)+(C38*2^14)+(D38*2^13)+(E38*2^12)+(F38*2^11)+(G38*2^10)+(H38*2^9)+(I38*2^8)+(J38*2^7)+(K38*2^6)+(L38*2^5)+(M38*2^4)+(N38*2^3)+(O38*2^2)+(P38*2^1)+(Q38*2^0),4)</f>
         <v>0x0004</v>
       </c>
-    </row>
-    <row r="39" spans="1:29">
+      <c r="AD38" s="16"/>
+    </row>
+    <row r="39" spans="1:30">
       <c r="A39" t="s">
         <v>2</v>
       </c>
@@ -2900,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="S39" s="6">
-        <f t="shared" ref="S39:S40" si="6" xml:space="preserve"> (-B39*2^15)+(C39*2^14)+(D39*2^13)+(E39*2^12)+(F39*2^11)+(G39*2^10)+(H39*2^9)+(I39*2^8)+(J39*2^7)+(K39*2^6)+(L39*2^5)+(M39*2^4)+(N39*2^3)+(O39*2^2)+(P39*2^1)+(Q39*2^0)</f>
+        <f t="shared" ref="S39" si="6" xml:space="preserve"> (-B39*2^15)+(C39*2^14)+(D39*2^13)+(E39*2^12)+(F39*2^11)+(G39*2^10)+(H39*2^9)+(I39*2^8)+(J39*2^7)+(K39*2^6)+(L39*2^5)+(M39*2^4)+(N39*2^3)+(O39*2^2)+(P39*2^1)+(Q39*2^0)</f>
         <v>3</v>
       </c>
       <c r="AA39" t="s">
@@ -2910,8 +2856,9 @@
         <f>"0x"&amp;DEC2HEX((B39*2^15)+(C39*2^14)+(D39*2^13)+(E39*2^12)+(F39*2^11)+(G39*2^10)+(H39*2^9)+(I39*2^8)+(J39*2^7)+(K39*2^6)+(L39*2^5)+(M39*2^4)+(N39*2^3)+(O39*2^2)+(P39*2^1)+(Q39*2^0),4)</f>
         <v>0x0003</v>
       </c>
-    </row>
-    <row r="40" spans="1:29">
+      <c r="AD39" s="16"/>
+    </row>
+    <row r="40" spans="1:30">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -2995,8 +2942,12 @@
         <f>"0x"&amp;DEC2HEX((B40*2^15)+(C40*2^14)+(D40*2^13)+(E40*2^12)+(F40*2^11)+(G40*2^10)+(H40*2^9)+(I40*2^8)+(J40*2^7)+(K40*2^6)+(L40*2^5)+(M40*2^4)+(N40*2^3)+(O40*2^2)+(P40*2^1)+(Q40*2^0),4)</f>
         <v>0x0001</v>
       </c>
-    </row>
-    <row r="42" spans="1:29">
+      <c r="AD40" s="16"/>
+    </row>
+    <row r="41" spans="1:30">
+      <c r="AD41" s="16"/>
+    </row>
+    <row r="42" spans="1:30">
       <c r="A42" t="s">
         <v>1</v>
       </c>
@@ -3059,8 +3010,9 @@
         <f>"0x"&amp;DEC2HEX((B42*2^15)+(C42*2^14)+(D42*2^13)+(E42*2^12)+(F42*2^11)+(G42*2^10)+(H42*2^9)+(I42*2^8)+(J42*2^7)+(K42*2^6)+(L42*2^5)+(M42*2^4)+(N42*2^3)+(O42*2^2)+(P42*2^1)+(Q42*2^0),4)</f>
         <v>0x0003</v>
       </c>
-    </row>
-    <row r="43" spans="1:29">
+      <c r="AD42" s="16"/>
+    </row>
+    <row r="43" spans="1:30">
       <c r="A43" t="s">
         <v>2</v>
       </c>
@@ -3113,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="6">
-        <f t="shared" ref="S43:S44" si="7" xml:space="preserve"> (-B43*2^15)+(C43*2^14)+(D43*2^13)+(E43*2^12)+(F43*2^11)+(G43*2^10)+(H43*2^9)+(I43*2^8)+(J43*2^7)+(K43*2^6)+(L43*2^5)+(M43*2^4)+(N43*2^3)+(O43*2^2)+(P43*2^1)+(Q43*2^0)</f>
+        <f t="shared" ref="S43" si="7" xml:space="preserve"> (-B43*2^15)+(C43*2^14)+(D43*2^13)+(E43*2^12)+(F43*2^11)+(G43*2^10)+(H43*2^9)+(I43*2^8)+(J43*2^7)+(K43*2^6)+(L43*2^5)+(M43*2^4)+(N43*2^3)+(O43*2^2)+(P43*2^1)+(Q43*2^0)</f>
         <v>4</v>
       </c>
       <c r="AA43" t="s">
@@ -3123,8 +3075,9 @@
         <f>"0x"&amp;DEC2HEX((B43*2^15)+(C43*2^14)+(D43*2^13)+(E43*2^12)+(F43*2^11)+(G43*2^10)+(H43*2^9)+(I43*2^8)+(J43*2^7)+(K43*2^6)+(L43*2^5)+(M43*2^4)+(N43*2^3)+(O43*2^2)+(P43*2^1)+(Q43*2^0),4)</f>
         <v>0x0004</v>
       </c>
-    </row>
-    <row r="44" spans="1:29">
+      <c r="AD43" s="16"/>
+    </row>
+    <row r="44" spans="1:30">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -3208,8 +3161,12 @@
         <f>"0x"&amp;DEC2HEX((B44*2^15)+(C44*2^14)+(D44*2^13)+(E44*2^12)+(F44*2^11)+(G44*2^10)+(H44*2^9)+(I44*2^8)+(J44*2^7)+(K44*2^6)+(L44*2^5)+(M44*2^4)+(N44*2^3)+(O44*2^2)+(P44*2^1)+(Q44*2^0),4)</f>
         <v>0xFFFF</v>
       </c>
-    </row>
-    <row r="46" spans="1:29">
+      <c r="AD44" s="16"/>
+    </row>
+    <row r="45" spans="1:30">
+      <c r="AD45" s="16"/>
+    </row>
+    <row r="46" spans="1:30">
       <c r="A46" t="s">
         <v>1</v>
       </c>
@@ -3272,8 +3229,9 @@
         <f>"0x"&amp;DEC2HEX((B46*2^15)+(C46*2^14)+(D46*2^13)+(E46*2^12)+(F46*2^11)+(G46*2^10)+(H46*2^9)+(I46*2^8)+(J46*2^7)+(K46*2^6)+(L46*2^5)+(M46*2^4)+(N46*2^3)+(O46*2^2)+(P46*2^1)+(Q46*2^0),4)</f>
         <v>0x0004</v>
       </c>
-    </row>
-    <row r="47" spans="1:29">
+      <c r="AD46" s="16"/>
+    </row>
+    <row r="47" spans="1:30">
       <c r="A47" t="s">
         <v>2</v>
       </c>
@@ -3326,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="6">
-        <f t="shared" ref="S47:S48" si="8" xml:space="preserve"> (-B47*2^15)+(C47*2^14)+(D47*2^13)+(E47*2^12)+(F47*2^11)+(G47*2^10)+(H47*2^9)+(I47*2^8)+(J47*2^7)+(K47*2^6)+(L47*2^5)+(M47*2^4)+(N47*2^3)+(O47*2^2)+(P47*2^1)+(Q47*2^0)</f>
+        <f t="shared" ref="S47" si="8" xml:space="preserve"> (-B47*2^15)+(C47*2^14)+(D47*2^13)+(E47*2^12)+(F47*2^11)+(G47*2^10)+(H47*2^9)+(I47*2^8)+(J47*2^7)+(K47*2^6)+(L47*2^5)+(M47*2^4)+(N47*2^3)+(O47*2^2)+(P47*2^1)+(Q47*2^0)</f>
         <v>4</v>
       </c>
       <c r="AA47" t="s">
@@ -3336,8 +3294,9 @@
         <f>"0x"&amp;DEC2HEX((B47*2^15)+(C47*2^14)+(D47*2^13)+(E47*2^12)+(F47*2^11)+(G47*2^10)+(H47*2^9)+(I47*2^8)+(J47*2^7)+(K47*2^6)+(L47*2^5)+(M47*2^4)+(N47*2^3)+(O47*2^2)+(P47*2^1)+(Q47*2^0),4)</f>
         <v>0x0004</v>
       </c>
-    </row>
-    <row r="48" spans="1:29">
+      <c r="AD47" s="16"/>
+    </row>
+    <row r="48" spans="1:30">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -3421,8 +3380,12 @@
         <f>"0x"&amp;DEC2HEX((B48*2^15)+(C48*2^14)+(D48*2^13)+(E48*2^12)+(F48*2^11)+(G48*2^10)+(H48*2^9)+(I48*2^8)+(J48*2^7)+(K48*2^6)+(L48*2^5)+(M48*2^4)+(N48*2^3)+(O48*2^2)+(P48*2^1)+(Q48*2^0),4)</f>
         <v>0x0000</v>
       </c>
-    </row>
-    <row r="50" spans="1:29">
+      <c r="AD48" s="16"/>
+    </row>
+    <row r="49" spans="1:30">
+      <c r="AD49" s="16"/>
+    </row>
+    <row r="50" spans="1:30">
       <c r="A50" t="s">
         <v>1</v>
       </c>
@@ -3482,8 +3445,9 @@
         <f>"0x"&amp;DEC2HEX((B50*2^15)+(C50*2^14)+(D50*2^13)+(E50*2^12)+(F50*2^11)+(G50*2^10)+(H50*2^9)+(I50*2^8)+(J50*2^7)+(K50*2^6)+(L50*2^5)+(M50*2^4)+(N50*2^3)+(O50*2^2)+(P50*2^1)+(Q50*2^0),4)</f>
         <v>0xFFFF</v>
       </c>
-    </row>
-    <row r="51" spans="1:29">
+      <c r="AD50" s="16"/>
+    </row>
+    <row r="51" spans="1:30">
       <c r="A51" t="s">
         <v>2</v>
       </c>
@@ -3536,15 +3500,16 @@
         <v>1</v>
       </c>
       <c r="S51" s="6">
-        <f t="shared" ref="S51:S52" si="9" xml:space="preserve"> (-B51*2^15)+(C51*2^14)+(D51*2^13)+(E51*2^12)+(F51*2^11)+(G51*2^10)+(H51*2^9)+(I51*2^8)+(J51*2^7)+(K51*2^6)+(L51*2^5)+(M51*2^4)+(N51*2^3)+(O51*2^2)+(P51*2^1)+(Q51*2^0)</f>
+        <f t="shared" ref="S51" si="9" xml:space="preserve"> (-B51*2^15)+(C51*2^14)+(D51*2^13)+(E51*2^12)+(F51*2^11)+(G51*2^10)+(H51*2^9)+(I51*2^8)+(J51*2^7)+(K51*2^6)+(L51*2^5)+(M51*2^4)+(N51*2^3)+(O51*2^2)+(P51*2^1)+(Q51*2^0)</f>
         <v>32767</v>
       </c>
       <c r="AC51" s="10" t="str">
         <f>"0x"&amp;DEC2HEX((B51*2^15)+(C51*2^14)+(D51*2^13)+(E51*2^12)+(F51*2^11)+(G51*2^10)+(H51*2^9)+(I51*2^8)+(J51*2^7)+(K51*2^6)+(L51*2^5)+(M51*2^4)+(N51*2^3)+(O51*2^2)+(P51*2^1)+(Q51*2^0),4)</f>
         <v>0x7FFF</v>
       </c>
-    </row>
-    <row r="52" spans="1:29">
+      <c r="AD51" s="16"/>
+    </row>
+    <row r="52" spans="1:30">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -3628,8 +3593,12 @@
         <f>"0x"&amp;DEC2HEX((B52*2^15)+(C52*2^14)+(D52*2^13)+(E52*2^12)+(F52*2^11)+(G52*2^10)+(H52*2^9)+(I52*2^8)+(J52*2^7)+(K52*2^6)+(L52*2^5)+(M52*2^4)+(N52*2^3)+(O52*2^2)+(P52*2^1)+(Q52*2^0),4)</f>
         <v>0x8000</v>
       </c>
-    </row>
-    <row r="54" spans="1:29">
+      <c r="AD52" s="16"/>
+    </row>
+    <row r="53" spans="1:30">
+      <c r="AD53" s="16"/>
+    </row>
+    <row r="54" spans="1:30">
       <c r="A54" t="s">
         <v>1</v>
       </c>
@@ -3689,8 +3658,9 @@
         <f>"0x"&amp;DEC2HEX((B54*2^15)+(C54*2^14)+(D54*2^13)+(E54*2^12)+(F54*2^11)+(G54*2^10)+(H54*2^9)+(I54*2^8)+(J54*2^7)+(K54*2^6)+(L54*2^5)+(M54*2^4)+(N54*2^3)+(O54*2^2)+(P54*2^1)+(Q54*2^0),4)</f>
         <v>0xBFFF</v>
       </c>
-    </row>
-    <row r="55" spans="1:29">
+      <c r="AD54" s="16"/>
+    </row>
+    <row r="55" spans="1:30">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -3743,15 +3713,16 @@
         <v>0</v>
       </c>
       <c r="S55" s="6">
-        <f t="shared" ref="S55:S56" si="10" xml:space="preserve"> (-B55*2^15)+(C55*2^14)+(D55*2^13)+(E55*2^12)+(F55*2^11)+(G55*2^10)+(H55*2^9)+(I55*2^8)+(J55*2^7)+(K55*2^6)+(L55*2^5)+(M55*2^4)+(N55*2^3)+(O55*2^2)+(P55*2^1)+(Q55*2^0)</f>
+        <f t="shared" ref="S55" si="10" xml:space="preserve"> (-B55*2^15)+(C55*2^14)+(D55*2^13)+(E55*2^12)+(F55*2^11)+(G55*2^10)+(H55*2^9)+(I55*2^8)+(J55*2^7)+(K55*2^6)+(L55*2^5)+(M55*2^4)+(N55*2^3)+(O55*2^2)+(P55*2^1)+(Q55*2^0)</f>
         <v>16384</v>
       </c>
       <c r="AC55" s="10" t="str">
         <f>"0x"&amp;DEC2HEX((B55*2^15)+(C55*2^14)+(D55*2^13)+(E55*2^12)+(F55*2^11)+(G55*2^10)+(H55*2^9)+(I55*2^8)+(J55*2^7)+(K55*2^6)+(L55*2^5)+(M55*2^4)+(N55*2^3)+(O55*2^2)+(P55*2^1)+(Q55*2^0),4)</f>
         <v>0x4000</v>
       </c>
-    </row>
-    <row r="56" spans="1:29">
+      <c r="AD55" s="16"/>
+    </row>
+    <row r="56" spans="1:30">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -3835,6 +3806,7 @@
         <f>"0x"&amp;DEC2HEX((B56*2^15)+(C56*2^14)+(D56*2^13)+(E56*2^12)+(F56*2^11)+(G56*2^10)+(H56*2^9)+(I56*2^8)+(J56*2^7)+(K56*2^6)+(L56*2^5)+(M56*2^4)+(N56*2^3)+(O56*2^2)+(P56*2^1)+(Q56*2^0),4)</f>
         <v>0x7FFF</v>
       </c>
+      <c r="AD56" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="S4">
@@ -3915,7 +3887,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3924,7 +3896,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
